--- a/hira_material_automation/output/monthly/202601_202607__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__temporary_synovial_substitute__250099__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:02:09</t>
+          <t>2026-07-14T22:02:01</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d2d323a6766cf87310b4f80ae8c0a29e933ec70f2167e0ba70c9c48be698a930</t>
+          <t>b06b45c5997beb36ad8fe456750f50681c628194aed75297991b69ef04f7f123</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__temporary_synovial_substitute__250099__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:02:01</t>
+          <t>2026-07-24T22:08:55</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b06b45c5997beb36ad8fe456750f50681c628194aed75297991b69ef04f7f123</t>
+          <t>e73afb85a4421e62cb41492804a00c528100c1316a3b44ce25087caaaad2f681</t>
         </is>
       </c>
     </row>
